--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.14-information-transfer/WKBK/90_workbooks/ISMS-IMP-A.5.14.1_Transfer_Rules_and_Procedures_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.14-information-transfer/WKBK/90_workbooks/ISMS-IMP-A.5.14.1_Transfer_Rules_and_Procedures_20260208.xlsx
@@ -1853,7 +1853,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Azure AD SSO</t>
+          <t>Microsoft Entra ID (formerly Azure AD) SSO</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Azure AD + MFA</t>
+          <t>Microsoft Entra ID (formerly Azure AD) + MFA</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Azure AD + MFA</t>
+          <t>Microsoft Entra ID (formerly Azure AD) + MFA</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Azure AD + MFA</t>
+          <t>Microsoft Entra ID (formerly Azure AD) + MFA</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Azure AD authentication</t>
+          <t>Microsoft Entra ID (formerly Azure AD) authentication</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
